--- a/my_response_pseudospectrum.xlsx
+++ b/my_response_pseudospectrum.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B301"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2828,6 +2828,806 @@
         <v>0.12415</v>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>3.00001</v>
+      </c>
+      <c r="B302" t="n">
+        <v>0.1228</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>3.01001</v>
+      </c>
+      <c r="B303" t="n">
+        <v>0.12143</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>3.02001</v>
+      </c>
+      <c r="B304" t="n">
+        <v>0.1201</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>3.03001</v>
+      </c>
+      <c r="B305" t="n">
+        <v>0.11873</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>3.04001</v>
+      </c>
+      <c r="B306" t="n">
+        <v>0.11736</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>3.05001</v>
+      </c>
+      <c r="B307" t="n">
+        <v>0.11601</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>3.06001</v>
+      </c>
+      <c r="B308" t="n">
+        <v>0.11462</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>3.07001</v>
+      </c>
+      <c r="B309" t="n">
+        <v>0.11324</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>3.08001</v>
+      </c>
+      <c r="B310" t="n">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>3.09001</v>
+      </c>
+      <c r="B311" t="n">
+        <v>0.11079</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>3.10001</v>
+      </c>
+      <c r="B312" t="n">
+        <v>0.1099</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>3.11001</v>
+      </c>
+      <c r="B313" t="n">
+        <v>0.10981</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>3.12001</v>
+      </c>
+      <c r="B314" t="n">
+        <v>0.10974</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>3.13001</v>
+      </c>
+      <c r="B315" t="n">
+        <v>0.10963</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>3.14001</v>
+      </c>
+      <c r="B316" t="n">
+        <v>0.1095</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>3.15001</v>
+      </c>
+      <c r="B317" t="n">
+        <v>0.10934</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>3.16001</v>
+      </c>
+      <c r="B318" t="n">
+        <v>0.10915</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>3.17001</v>
+      </c>
+      <c r="B319" t="n">
+        <v>0.10894</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>3.18001</v>
+      </c>
+      <c r="B320" t="n">
+        <v>0.10874</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>3.19001</v>
+      </c>
+      <c r="B321" t="n">
+        <v>0.10853</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>3.20001</v>
+      </c>
+      <c r="B322" t="n">
+        <v>0.1083</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>3.21001</v>
+      </c>
+      <c r="B323" t="n">
+        <v>0.10804</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>3.22001</v>
+      </c>
+      <c r="B324" t="n">
+        <v>0.10775</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>3.23001</v>
+      </c>
+      <c r="B325" t="n">
+        <v>0.10744</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>3.24001</v>
+      </c>
+      <c r="B326" t="n">
+        <v>0.10711</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>3.25001</v>
+      </c>
+      <c r="B327" t="n">
+        <v>0.10681</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>3.26001</v>
+      </c>
+      <c r="B328" t="n">
+        <v>0.10649</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>3.27001</v>
+      </c>
+      <c r="B329" t="n">
+        <v>0.10615</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>3.28001</v>
+      </c>
+      <c r="B330" t="n">
+        <v>0.10579</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>3.29001</v>
+      </c>
+      <c r="B331" t="n">
+        <v>0.1054</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>3.30001</v>
+      </c>
+      <c r="B332" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>3.31001</v>
+      </c>
+      <c r="B333" t="n">
+        <v>0.10463</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>3.32001</v>
+      </c>
+      <c r="B334" t="n">
+        <v>0.10424</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>3.33001</v>
+      </c>
+      <c r="B335" t="n">
+        <v>0.10383</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>3.34001</v>
+      </c>
+      <c r="B336" t="n">
+        <v>0.1034</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>3.35001</v>
+      </c>
+      <c r="B337" t="n">
+        <v>0.10296</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>3.36001</v>
+      </c>
+      <c r="B338" t="n">
+        <v>0.10254</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>3.37001</v>
+      </c>
+      <c r="B339" t="n">
+        <v>0.10211</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>3.38001</v>
+      </c>
+      <c r="B340" t="n">
+        <v>0.10166</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>3.39001</v>
+      </c>
+      <c r="B341" t="n">
+        <v>0.10119</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>3.40001</v>
+      </c>
+      <c r="B342" t="n">
+        <v>0.10073</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>3.41001</v>
+      </c>
+      <c r="B343" t="n">
+        <v>0.10028</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>3.42001</v>
+      </c>
+      <c r="B344" t="n">
+        <v>0.09981</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3.43001</v>
+      </c>
+      <c r="B345" t="n">
+        <v>0.09933</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>3.44001</v>
+      </c>
+      <c r="B346" t="n">
+        <v>0.09883</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>3.45001</v>
+      </c>
+      <c r="B347" t="n">
+        <v>0.09832</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>3.46001</v>
+      </c>
+      <c r="B348" t="n">
+        <v>0.09782</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>3.47001</v>
+      </c>
+      <c r="B349" t="n">
+        <v>0.09733</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>3.48001</v>
+      </c>
+      <c r="B350" t="n">
+        <v>0.09682</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3.49001</v>
+      </c>
+      <c r="B351" t="n">
+        <v>0.0963</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3.50001</v>
+      </c>
+      <c r="B352" t="n">
+        <v>0.09576</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>3.51001</v>
+      </c>
+      <c r="B353" t="n">
+        <v>0.09522</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>3.52001</v>
+      </c>
+      <c r="B354" t="n">
+        <v>0.09465999999999999</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>3.53001</v>
+      </c>
+      <c r="B355" t="n">
+        <v>0.09408999999999999</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>3.54001</v>
+      </c>
+      <c r="B356" t="n">
+        <v>0.09354</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>3.55001</v>
+      </c>
+      <c r="B357" t="n">
+        <v>0.09299</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>3.56001</v>
+      </c>
+      <c r="B358" t="n">
+        <v>0.09243</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>3.57001</v>
+      </c>
+      <c r="B359" t="n">
+        <v>0.09186</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>3.58001</v>
+      </c>
+      <c r="B360" t="n">
+        <v>0.09128</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>3.59001</v>
+      </c>
+      <c r="B361" t="n">
+        <v>0.09069000000000001</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>3.60001</v>
+      </c>
+      <c r="B362" t="n">
+        <v>0.09009</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>3.61001</v>
+      </c>
+      <c r="B363" t="n">
+        <v>0.08948</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>3.62001</v>
+      </c>
+      <c r="B364" t="n">
+        <v>0.08887</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>3.63001</v>
+      </c>
+      <c r="B365" t="n">
+        <v>0.08825</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>3.64001</v>
+      </c>
+      <c r="B366" t="n">
+        <v>0.08764</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>3.65001</v>
+      </c>
+      <c r="B367" t="n">
+        <v>0.08704000000000001</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>3.66001</v>
+      </c>
+      <c r="B368" t="n">
+        <v>0.08643000000000001</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>3.67001</v>
+      </c>
+      <c r="B369" t="n">
+        <v>0.08581999999999999</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>3.68001</v>
+      </c>
+      <c r="B370" t="n">
+        <v>0.08519</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>3.69001</v>
+      </c>
+      <c r="B371" t="n">
+        <v>0.08457000000000001</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>3.70001</v>
+      </c>
+      <c r="B372" t="n">
+        <v>0.08393</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>3.71001</v>
+      </c>
+      <c r="B373" t="n">
+        <v>0.08329</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>3.72001</v>
+      </c>
+      <c r="B374" t="n">
+        <v>0.08265</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>3.73001</v>
+      </c>
+      <c r="B375" t="n">
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>3.74001</v>
+      </c>
+      <c r="B376" t="n">
+        <v>0.08136</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>3.75001</v>
+      </c>
+      <c r="B377" t="n">
+        <v>0.08073</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>3.76001</v>
+      </c>
+      <c r="B378" t="n">
+        <v>0.0801</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>3.77001</v>
+      </c>
+      <c r="B379" t="n">
+        <v>0.07946</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>3.78001</v>
+      </c>
+      <c r="B380" t="n">
+        <v>0.07882</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>3.79001</v>
+      </c>
+      <c r="B381" t="n">
+        <v>0.07817</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>3.80001</v>
+      </c>
+      <c r="B382" t="n">
+        <v>0.07753</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>3.81001</v>
+      </c>
+      <c r="B383" t="n">
+        <v>0.07686999999999999</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>3.82001</v>
+      </c>
+      <c r="B384" t="n">
+        <v>0.07622</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>3.83001</v>
+      </c>
+      <c r="B385" t="n">
+        <v>0.07557</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>3.84001</v>
+      </c>
+      <c r="B386" t="n">
+        <v>0.07493</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>3.85001</v>
+      </c>
+      <c r="B387" t="n">
+        <v>0.07428999999999999</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>3.86001</v>
+      </c>
+      <c r="B388" t="n">
+        <v>0.07364999999999999</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>3.87001</v>
+      </c>
+      <c r="B389" t="n">
+        <v>0.07301000000000001</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>3.88001</v>
+      </c>
+      <c r="B390" t="n">
+        <v>0.07235999999999999</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>3.89001</v>
+      </c>
+      <c r="B391" t="n">
+        <v>0.07172000000000001</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>3.90001</v>
+      </c>
+      <c r="B392" t="n">
+        <v>0.07106999999999999</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>3.91001</v>
+      </c>
+      <c r="B393" t="n">
+        <v>0.07042</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>3.92001</v>
+      </c>
+      <c r="B394" t="n">
+        <v>0.06979</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>3.93001</v>
+      </c>
+      <c r="B395" t="n">
+        <v>0.06916</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>3.94001</v>
+      </c>
+      <c r="B396" t="n">
+        <v>0.06852</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>3.95001</v>
+      </c>
+      <c r="B397" t="n">
+        <v>0.06789000000000001</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>3.96001</v>
+      </c>
+      <c r="B398" t="n">
+        <v>0.06726</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>3.97001</v>
+      </c>
+      <c r="B399" t="n">
+        <v>0.06662999999999999</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>3.98001</v>
+      </c>
+      <c r="B400" t="n">
+        <v>0.06598999999999999</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>3.99001</v>
+      </c>
+      <c r="B401" t="n">
+        <v>0.06537</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
